--- a/04_fulltext/fullTextScreening.xlsx
+++ b/04_fulltext/fullTextScreening.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arjen/kDrive/Obsidian/Literature Review MDIM/04_fulltext/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E354F3B-A6D1-CB49-BCB0-97483824F466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3DDE09-82A1-8547-A5DB-D5DEF28A6990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Exclusiecriteria" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full Text Scores'!$A$1:$I$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full Text Scores'!$A$1:$I$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="279">
   <si>
     <t>Auteur(s) en Jaar</t>
   </si>
@@ -601,6 +601,279 @@
   </si>
   <si>
     <t>4D-SETL a semantic data integration framework</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>On Thesaurus mapping only</t>
+  </si>
+  <si>
+    <t>On OOTS</t>
+  </si>
+  <si>
+    <t>Focussed on service delivery in Tunesia and very implementatiom oriented</t>
+  </si>
+  <si>
+    <t>Focussed on one system design for BIM implementation</t>
+  </si>
+  <si>
+    <t>UML Design on GEO Information in Turkey</t>
+  </si>
+  <si>
+    <t>Shallow insights in deployment of Linked Data in Thailand</t>
+  </si>
+  <si>
+    <t>Very much focussed on the design process of government ontlogies</t>
+  </si>
+  <si>
+    <t>Promissing but the core of the approach is missing/very weak</t>
+  </si>
+  <si>
+    <t>Shallow report on the devlopment of a UN Geo taxonomy</t>
+  </si>
+  <si>
+    <t>Focus is teh dynamics of government ontologies and how to integrate these</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In depth description of mediation approach </t>
+  </si>
+  <si>
+    <t>Extensive definitions on semantic interoperability artefacts</t>
+  </si>
+  <si>
+    <t>More of a architectural description</t>
+  </si>
+  <si>
+    <t>Semantic Framework to classify and interprete Archive (and broader) documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metadata application in Teheran </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reports an urban fault system for citicens </t>
+  </si>
+  <si>
+    <t>Three types of semantic integration in Russia</t>
+  </si>
+  <si>
+    <t>On automated tagging</t>
+  </si>
+  <si>
+    <t>terminilogical interoperability in a health setting</t>
+  </si>
+  <si>
+    <t>Introduction of a crop vocabulary in Japan linking it to others</t>
+  </si>
+  <si>
+    <t>System Description of CAMELOT (Unmand Aerial System Control)</t>
+  </si>
+  <si>
+    <t>Indian generic datamodel that is being used to gather staistical data</t>
+  </si>
+  <si>
+    <t>Designing An Ecosystem Model for E-Government  Ontology Development Using Ecosystem Pie Model</t>
+  </si>
+  <si>
+    <t>Dri Kurniawan (2022)</t>
+  </si>
+  <si>
+    <t>Pie model gives new perspective on looking at government services</t>
+  </si>
+  <si>
+    <t>Case Study</t>
+  </si>
+  <si>
+    <t>Mainly description of ELMO ontology</t>
+  </si>
+  <si>
+    <t>Case Study of Bhutans BTNAD Ontology</t>
+  </si>
+  <si>
+    <t>Describes how to identify patients over multiple domains</t>
+  </si>
+  <si>
+    <t>MDIM Case Study</t>
+  </si>
+  <si>
+    <t>Describes Estoniam Xroad and the way multiple ontologies are combined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outlines State of INSPIRE Directive </t>
+  </si>
+  <si>
+    <t>Describes Semantic Smckdown methodology for developing ontologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses the case of a violant crime process ontology to show how to break up in multiple ontlogies </t>
+  </si>
+  <si>
+    <t>Lit Review on generic data models</t>
+  </si>
+  <si>
+    <t>NATO Use Case for semantic interoperability</t>
+  </si>
+  <si>
+    <t>Academic project in Taiwan on creating a government ontology combined with a thesaurus</t>
+  </si>
+  <si>
+    <t>On performance of large scale integration of semantic datasets (allmost off topic)</t>
+  </si>
+  <si>
+    <t>On combining Spanish and Portugees datasets on forrests</t>
+  </si>
+  <si>
+    <t>Rgorous approach to information sharing and combining in a maratime setting</t>
+  </si>
+  <si>
+    <t>Use of Semantic Description model in Tawain</t>
+  </si>
+  <si>
+    <t>Connecting data using a knowledge graph</t>
+  </si>
+  <si>
+    <t>Using knowlege graphs to connect semantics</t>
+  </si>
+  <si>
+    <t>Alqahtani e.a. (2014)</t>
+  </si>
+  <si>
+    <t>Knowledge-based life event model for e-government service integration with illustrative examples</t>
+  </si>
+  <si>
+    <t>Using a ontology for life events in Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Pro Rail Semantic interoperability using ontlogies and Knwoledge management</t>
+  </si>
+  <si>
+    <t>Investigates different library (books) schema's and how they are interoperable</t>
+  </si>
+  <si>
+    <t>On merging of databases: design steps of one system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very strong overview of how models are used in a government setting. Spans further than semantic interoperability only </t>
+  </si>
+  <si>
+    <t>FAA (Aviation) challenges with combining data form different sources and a ontlogy approach to tackle these challenges</t>
+  </si>
+  <si>
+    <t>Maroccon ontology approach with few insights</t>
+  </si>
+  <si>
+    <t>On the use of ontologies to conceptualize domain knowledge</t>
+  </si>
+  <si>
+    <t>Combining legal terminology in order to provide better service to the public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On copy right problems using open biodeversity taxonomies </t>
+  </si>
+  <si>
+    <t>Description of Belgian OSLO initiative: very relevant</t>
+  </si>
+  <si>
+    <t>On harmonization of EU language lexicons</t>
+  </si>
+  <si>
+    <t>Smart cities with heterogenous datasources, the case of Catania</t>
+  </si>
+  <si>
+    <t>Totaal groen:</t>
+  </si>
+  <si>
+    <t>Totaal geel</t>
+  </si>
+  <si>
+    <t>Totaal rood:</t>
+  </si>
+  <si>
+    <t>EU ESSSI Project: On using vocabularies (taxanomies) to solve semantic conflics  in social security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IoT interoperability in Japan </t>
+  </si>
+  <si>
+    <t>Interoperability of Base Registries in Flandres connected to OSLO with description of Base Registries in other EU conountroes</t>
+  </si>
+  <si>
+    <t>Integration of Norwegian cadastral ssystem and landowner system with integration hub</t>
+  </si>
+  <si>
+    <t>On Enhancing Quality in Legal Information Indexing. Focussed on multi lingual issues</t>
+  </si>
+  <si>
+    <t>On combining different legal ontologies</t>
+  </si>
+  <si>
+    <t>Describes Estionians X-Road</t>
+  </si>
+  <si>
+    <t>Describes the inner workings of the BRITE system when merging ontologies</t>
+  </si>
+  <si>
+    <t>Defines the structure of an architecture</t>
+  </si>
+  <si>
+    <t>Semantic technologies for e-government</t>
+  </si>
+  <si>
+    <t>Vitvar e.a. (2010)</t>
+  </si>
+  <si>
+    <t>Describes sub sharan government domain ontology</t>
+  </si>
+  <si>
+    <t>Mapping of thesauri using A</t>
+  </si>
+  <si>
+    <t>Semantic interoperability from a social science perspective</t>
+  </si>
+  <si>
+    <t>Analyses of the use of the EU Core Vocabularies</t>
+  </si>
+  <si>
+    <t>On semantic aspects of cross EU communication of Eduction information/proof</t>
+  </si>
+  <si>
+    <t>On open data in Teheran with an explict implementation</t>
+  </si>
+  <si>
+    <t>Lit. review on how ontlologies can enahce e-government</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describes a public service ontology </t>
+  </si>
+  <si>
+    <t>Thorough anaysis of interoperability issues in BIM</t>
+  </si>
+  <si>
+    <t>Methodology for developing ontlogies for FAIR EU Data Spaces</t>
+  </si>
+  <si>
+    <t>Focus on buildung a BIO Bank</t>
+  </si>
+  <si>
+    <t>Data integrations and challenges shown with a forrest fire system</t>
+  </si>
+  <si>
+    <t>On lexical integration in the EU</t>
+  </si>
+  <si>
+    <t>Semantic aspects of combining health services</t>
+  </si>
+  <si>
+    <t>Towards building a semantic grid for E-government applications</t>
+  </si>
+  <si>
+    <t>Zhang e.a. (2008)</t>
+  </si>
+  <si>
+    <t>Semantic Grid infrastructure to support distributed e-government applications</t>
+  </si>
+  <si>
+    <t>ontological description of land use</t>
   </si>
 </sst>
 </file>
@@ -783,7 +1056,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -823,14 +1096,120 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -1956,7 +2335,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="33.5" style="2" bestFit="1" customWidth="1"/>
@@ -1968,11 +2347,12 @@
     <col min="7" max="7" width="41.1640625" style="2" customWidth="1"/>
     <col min="8" max="8" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="48" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.33203125" style="2"/>
+    <col min="10" max="10" width="117" style="2" customWidth="1"/>
+    <col min="11" max="11" width="28.1640625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2000,798 +2380,1296 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J1" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>187</v>
+        <v>25</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="5">
         <v>2</v>
       </c>
       <c r="E2" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="5">
         <v>2</v>
       </c>
       <c r="H2" s="5">
         <f>SUM(D2:G2)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+    </row>
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5">
         <f>SUM(D3:G3)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I3" s="10"/>
-    </row>
-    <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C4" s="11"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="D4" s="9">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>2</v>
+      </c>
       <c r="H4" s="5">
         <f>SUM(D4:G4)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J4" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="K4" s="15"/>
+    </row>
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="D5" s="9">
+        <v>2</v>
+      </c>
+      <c r="E5" s="9">
+        <v>2</v>
+      </c>
+      <c r="F5" s="9">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9">
+        <v>2</v>
+      </c>
       <c r="H5" s="5">
         <f>SUM(D5:G5)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I5" s="10"/>
-    </row>
-    <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J5" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="D6" s="9">
+        <v>2</v>
+      </c>
+      <c r="E6" s="9">
+        <v>2</v>
+      </c>
+      <c r="F6" s="9">
+        <v>2</v>
+      </c>
+      <c r="G6" s="9">
+        <v>2</v>
+      </c>
       <c r="H6" s="5">
         <f>SUM(D6:G6)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I6" s="10"/>
-    </row>
-    <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J6" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C7" s="11"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="D7" s="9">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9">
+        <v>2</v>
+      </c>
+      <c r="G7" s="9">
+        <v>2</v>
+      </c>
       <c r="H7" s="5">
         <f>SUM(D7:G7)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I7" s="10"/>
-    </row>
-    <row r="8" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J7" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="D8" s="9">
+        <v>2</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2</v>
+      </c>
+      <c r="F8" s="9">
+        <v>2</v>
+      </c>
+      <c r="G8" s="9">
+        <v>2</v>
+      </c>
       <c r="H8" s="5">
         <f>SUM(D8:G8)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J8" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="D9" s="9">
+        <v>2</v>
+      </c>
+      <c r="E9" s="9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="9">
+        <v>2</v>
+      </c>
       <c r="H9" s="5">
         <f>SUM(D9:G9)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J9" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="D10" s="9">
+        <v>2</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2</v>
+      </c>
+      <c r="F10" s="9">
+        <v>1</v>
+      </c>
+      <c r="G10" s="9">
+        <v>2</v>
+      </c>
       <c r="H10" s="5">
         <f>SUM(D10:G10)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J10" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2</v>
+      </c>
+      <c r="F11" s="9">
+        <v>2</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1</v>
+      </c>
       <c r="H11" s="5">
         <f>SUM(D11:G11)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I11" s="10"/>
-    </row>
-    <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J11" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="D12" s="9">
+        <v>2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1</v>
+      </c>
+      <c r="F12" s="9">
+        <v>2</v>
+      </c>
+      <c r="G12" s="9">
+        <v>2</v>
+      </c>
       <c r="H12" s="5">
         <f>SUM(D12:G12)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J12" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="D13" s="9">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9">
+        <v>2</v>
+      </c>
+      <c r="G13" s="9">
+        <v>2</v>
+      </c>
       <c r="H13" s="5">
         <f>SUM(D13:G13)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J13" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="D14" s="9">
+        <v>2</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2</v>
+      </c>
+      <c r="F14" s="9">
+        <v>1</v>
+      </c>
+      <c r="G14" s="9">
+        <v>2</v>
+      </c>
       <c r="H14" s="5">
         <f>SUM(D14:G14)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J14" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="C15" s="11"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="D15" s="9">
+        <v>2</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1</v>
+      </c>
+      <c r="G15" s="9">
+        <v>2</v>
+      </c>
       <c r="H15" s="5">
         <f>SUM(D15:G15)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J15" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>146</v>
+        <v>212</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="C16" s="11"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="D16" s="9">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9">
+        <v>2</v>
+      </c>
+      <c r="F16" s="9">
+        <v>2</v>
+      </c>
+      <c r="G16" s="9">
+        <v>2</v>
+      </c>
       <c r="H16" s="5">
         <f>SUM(D16:G16)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I16" s="10"/>
-    </row>
-    <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J16" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="K16" s="15"/>
+    </row>
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C17" s="11"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="D17" s="9">
+        <v>2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9">
+        <v>2</v>
+      </c>
+      <c r="G17" s="9">
+        <v>2</v>
+      </c>
       <c r="H17" s="5">
         <f>SUM(D17:G17)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="C18" s="11"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="D18" s="9">
+        <v>2</v>
+      </c>
+      <c r="E18" s="9">
+        <v>2</v>
+      </c>
+      <c r="F18" s="9">
+        <v>1</v>
+      </c>
+      <c r="G18" s="9">
+        <v>2</v>
+      </c>
       <c r="H18" s="5">
         <f>SUM(D18:G18)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I18" s="10"/>
-    </row>
-    <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+    </row>
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
-        <v>60</v>
+        <v>166</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="C19" s="11"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="D19" s="9">
+        <v>2</v>
+      </c>
+      <c r="E19" s="9">
+        <v>2</v>
+      </c>
+      <c r="F19" s="9">
+        <v>1</v>
+      </c>
+      <c r="G19" s="9">
+        <v>2</v>
+      </c>
       <c r="H19" s="5">
         <f>SUM(D19:G19)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I19" s="10"/>
-    </row>
-    <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J19" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="K19" s="15"/>
+    </row>
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C20" s="11"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="D20" s="9">
+        <v>2</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2</v>
+      </c>
+      <c r="F20" s="9">
+        <v>2</v>
+      </c>
+      <c r="G20" s="9">
+        <v>1</v>
+      </c>
       <c r="H20" s="5">
         <f>SUM(D20:G20)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="C21" s="11"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="D21" s="9">
+        <v>2</v>
+      </c>
+      <c r="E21" s="9">
+        <v>2</v>
+      </c>
+      <c r="F21" s="9">
+        <v>2</v>
+      </c>
+      <c r="G21" s="9">
+        <v>1</v>
+      </c>
       <c r="H21" s="5">
         <f>SUM(D21:G21)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J21" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="K21" s="15"/>
+    </row>
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="C22" s="11"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="D22" s="9">
+        <v>2</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1</v>
+      </c>
+      <c r="G22" s="9">
+        <v>2</v>
+      </c>
       <c r="H22" s="5">
         <f>SUM(D22:G22)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J22" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="K22" s="15"/>
+    </row>
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="C23" s="11"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="D23" s="9">
+        <v>1</v>
+      </c>
+      <c r="E23" s="9">
+        <v>2</v>
+      </c>
+      <c r="F23" s="9">
+        <v>2</v>
+      </c>
+      <c r="G23" s="9">
+        <v>2</v>
+      </c>
       <c r="H23" s="5">
         <f>SUM(D23:G23)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I23" s="10"/>
-    </row>
-    <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J23" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="C24" s="11"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="D24" s="9">
+        <v>2</v>
+      </c>
+      <c r="E24" s="9">
+        <v>2</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1</v>
+      </c>
+      <c r="G24" s="9">
+        <v>2</v>
+      </c>
       <c r="H24" s="5">
         <f>SUM(D24:G24)</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="13"/>
-    </row>
-    <row r="25" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="I24" s="10"/>
+      <c r="J24" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="K24" s="15"/>
+    </row>
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="C25" s="11"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="D25" s="9">
+        <v>2</v>
+      </c>
+      <c r="E25" s="9">
+        <v>2</v>
+      </c>
+      <c r="F25" s="9">
+        <v>1</v>
+      </c>
+      <c r="G25" s="9">
+        <v>2</v>
+      </c>
       <c r="H25" s="5">
         <f>SUM(D25:G25)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I25" s="10"/>
-    </row>
-    <row r="26" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J25" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="K25" s="15"/>
+    </row>
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C26" s="11"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="D26" s="9">
+        <v>2</v>
+      </c>
+      <c r="E26" s="9">
+        <v>2</v>
+      </c>
+      <c r="F26" s="9">
+        <v>1</v>
+      </c>
+      <c r="G26" s="9">
+        <v>2</v>
+      </c>
       <c r="H26" s="5">
         <f>SUM(D26:G26)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I26" s="10"/>
-    </row>
-    <row r="27" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J26" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K26" s="15"/>
+    </row>
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="C27" s="11"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="D27" s="9">
+        <v>2</v>
+      </c>
+      <c r="E27" s="9">
+        <v>2</v>
+      </c>
+      <c r="F27" s="9">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9">
+        <v>2</v>
+      </c>
       <c r="H27" s="5">
         <f>SUM(D27:G27)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I27" s="10"/>
-    </row>
-    <row r="28" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="C28" s="11"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="D28" s="9">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9">
+        <v>2</v>
+      </c>
+      <c r="F28" s="9">
+        <v>2</v>
+      </c>
+      <c r="G28" s="9">
+        <v>2</v>
+      </c>
       <c r="H28" s="5">
         <f>SUM(D28:G28)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I28" s="10"/>
-    </row>
-    <row r="29" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J28" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="K28" s="15"/>
+    </row>
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="C29" s="11"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
+      <c r="D29" s="9">
+        <v>2</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1</v>
+      </c>
+      <c r="F29" s="9">
+        <v>2</v>
+      </c>
+      <c r="G29" s="9">
+        <v>2</v>
+      </c>
       <c r="H29" s="5">
         <f>SUM(D29:G29)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I29" s="10"/>
-    </row>
-    <row r="30" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J29" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C30" s="11"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
+      <c r="D30" s="9">
+        <v>2</v>
+      </c>
+      <c r="E30" s="9">
+        <v>2</v>
+      </c>
+      <c r="F30" s="9">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9">
+        <v>2</v>
+      </c>
       <c r="H30" s="5">
         <f>SUM(D30:G30)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I30" s="10"/>
-    </row>
-    <row r="31" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J30" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="K30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C31" s="11"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="D31" s="9">
+        <v>2</v>
+      </c>
+      <c r="E31" s="9">
+        <v>2</v>
+      </c>
+      <c r="F31" s="9">
+        <v>1</v>
+      </c>
+      <c r="G31" s="9">
+        <v>2</v>
+      </c>
       <c r="H31" s="5">
         <f>SUM(D31:G31)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I31" s="10"/>
-    </row>
-    <row r="32" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+    </row>
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
+        <v>143</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D32" s="9">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9">
+        <v>2</v>
+      </c>
+      <c r="F32" s="9">
+        <v>2</v>
+      </c>
+      <c r="G32" s="9">
+        <v>2</v>
+      </c>
       <c r="H32" s="5">
         <f>SUM(D32:G32)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I32" s="10"/>
-    </row>
-    <row r="33" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="C33" s="11"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
+      <c r="D33" s="9">
+        <v>2</v>
+      </c>
+      <c r="E33" s="9">
+        <v>2</v>
+      </c>
+      <c r="F33" s="9">
+        <v>2</v>
+      </c>
+      <c r="G33" s="9">
+        <v>1</v>
+      </c>
       <c r="H33" s="5">
         <f>SUM(D33:G33)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I33" s="10"/>
-    </row>
-    <row r="34" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="C34" s="11"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="D34" s="9">
+        <v>2</v>
+      </c>
+      <c r="E34" s="9">
+        <v>2</v>
+      </c>
+      <c r="F34" s="9">
+        <v>1</v>
+      </c>
+      <c r="G34" s="9">
+        <v>2</v>
+      </c>
       <c r="H34" s="5">
         <f>SUM(D34:G34)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I34" s="10"/>
-    </row>
-    <row r="35" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J34" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="C35" s="11"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
+      <c r="D35" s="9">
+        <v>2</v>
+      </c>
+      <c r="E35" s="9">
+        <v>2</v>
+      </c>
+      <c r="F35" s="9">
+        <v>1</v>
+      </c>
+      <c r="G35" s="9">
+        <v>2</v>
+      </c>
       <c r="H35" s="5">
         <f>SUM(D35:G35)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I35" s="10"/>
-    </row>
-    <row r="36" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+    </row>
+    <row r="36" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C36" s="11"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="D36" s="9">
+        <v>2</v>
+      </c>
+      <c r="E36" s="9">
+        <v>2</v>
+      </c>
+      <c r="F36" s="9">
+        <v>1</v>
+      </c>
+      <c r="G36" s="9">
+        <v>2</v>
+      </c>
       <c r="H36" s="5">
         <f>SUM(D36:G36)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I36" s="10"/>
-    </row>
-    <row r="37" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J36" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
-        <v>52</v>
+        <v>186</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="C37" s="11"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="D37" s="9">
+        <v>2</v>
+      </c>
+      <c r="E37" s="9">
+        <v>1</v>
+      </c>
+      <c r="F37" s="9">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9">
+        <v>2</v>
+      </c>
       <c r="H37" s="5">
         <f>SUM(D37:G37)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I37" s="10"/>
-    </row>
-    <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J37" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C38" s="11"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="D38" s="9">
+        <v>1</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1</v>
+      </c>
+      <c r="F38" s="9">
+        <v>2</v>
+      </c>
+      <c r="G38" s="9">
+        <v>2</v>
+      </c>
       <c r="H38" s="5">
         <f>SUM(D38:G38)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I38" s="10"/>
-    </row>
-    <row r="39" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J38" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="K38" s="15"/>
+    </row>
+    <row r="39" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="C39" s="11"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="D39" s="9">
+        <v>2</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1</v>
+      </c>
+      <c r="F39" s="9">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
+        <v>2</v>
+      </c>
       <c r="H39" s="5">
         <f>SUM(D39:G39)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I39" s="10"/>
-    </row>
-    <row r="40" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J39" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="7" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="C40" s="11"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
+      <c r="D40" s="9">
+        <v>2</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9">
+        <v>2</v>
+      </c>
       <c r="H40" s="5">
         <f>SUM(D40:G40)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I40" s="10"/>
-    </row>
-    <row r="41" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J40" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="K40" s="15"/>
+    </row>
+    <row r="41" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7" t="s">
-        <v>48</v>
+        <v>176</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="C41" s="11"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="D41" s="9">
+        <v>2</v>
+      </c>
+      <c r="E41" s="9">
+        <v>2</v>
+      </c>
+      <c r="F41" s="9">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9">
+        <v>1</v>
+      </c>
       <c r="H41" s="5">
         <f>SUM(D41:G41)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I41" s="10"/>
-    </row>
-    <row r="42" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J41" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="K41" s="15"/>
+    </row>
+    <row r="42" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="7" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="C42" s="11"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
+      <c r="D42" s="9">
+        <v>2</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1</v>
+      </c>
+      <c r="F42" s="9">
+        <v>1</v>
+      </c>
+      <c r="G42" s="9">
+        <v>2</v>
+      </c>
       <c r="H42" s="5">
         <f>SUM(D42:G42)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I42" s="10"/>
-    </row>
-    <row r="43" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J42" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="7" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C43" s="11"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
+      <c r="D43" s="9">
+        <v>2</v>
+      </c>
+      <c r="E43" s="9">
+        <v>2</v>
+      </c>
+      <c r="F43" s="9">
+        <v>1</v>
+      </c>
+      <c r="G43" s="9">
+        <v>1</v>
+      </c>
       <c r="H43" s="5">
         <f>SUM(D43:G43)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I43" s="10"/>
-    </row>
-    <row r="44" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J43" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="7" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C44" s="11"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
+      <c r="D44" s="9">
+        <v>2</v>
+      </c>
+      <c r="E44" s="9">
+        <v>1</v>
+      </c>
+      <c r="F44" s="9">
+        <v>1</v>
+      </c>
+      <c r="G44" s="9">
+        <v>2</v>
+      </c>
       <c r="H44" s="5">
         <f>SUM(D44:G44)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I44" s="10"/>
-    </row>
-    <row r="45" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J44" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="7" t="s">
         <v>120</v>
       </c>
@@ -2799,806 +3677,1536 @@
         <v>121</v>
       </c>
       <c r="C45" s="11"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
+      <c r="D45" s="9">
+        <v>1</v>
+      </c>
+      <c r="E45" s="9">
+        <v>1</v>
+      </c>
+      <c r="F45" s="9">
+        <v>2</v>
+      </c>
+      <c r="G45" s="9">
+        <v>2</v>
+      </c>
       <c r="H45" s="5">
         <f>SUM(D45:G45)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I45" s="10"/>
-    </row>
-    <row r="46" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J45" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="K45" s="15"/>
+    </row>
+    <row r="46" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="C46" s="11"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
+      <c r="D46" s="9">
+        <v>2</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1</v>
+      </c>
+      <c r="F46" s="9">
+        <v>2</v>
+      </c>
+      <c r="G46" s="9">
+        <v>1</v>
+      </c>
       <c r="H46" s="5">
         <f>SUM(D46:G46)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I46" s="10"/>
-    </row>
-    <row r="47" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J46" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K46" s="15"/>
+    </row>
+    <row r="47" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C47" s="11"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
+      <c r="D47" s="9">
+        <v>1</v>
+      </c>
+      <c r="E47" s="9">
+        <v>2</v>
+      </c>
+      <c r="F47" s="9">
+        <v>1</v>
+      </c>
+      <c r="G47" s="9">
+        <v>2</v>
+      </c>
       <c r="H47" s="5">
         <f>SUM(D47:G47)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I47" s="10"/>
-    </row>
-    <row r="48" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J47" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="7" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C48" s="11"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
+      <c r="D48" s="9">
+        <v>2</v>
+      </c>
+      <c r="E48" s="9">
+        <v>1</v>
+      </c>
+      <c r="F48" s="9">
+        <v>1</v>
+      </c>
+      <c r="G48" s="9">
+        <v>2</v>
+      </c>
       <c r="H48" s="5">
         <f>SUM(D48:G48)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I48" s="10"/>
-    </row>
-    <row r="49" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J48" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="K48" s="15"/>
+    </row>
+    <row r="49" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>28</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="C49" s="11"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
+      <c r="D49" s="9">
+        <v>1</v>
+      </c>
+      <c r="E49" s="9">
+        <v>1</v>
+      </c>
+      <c r="F49" s="9">
+        <v>1</v>
+      </c>
+      <c r="G49" s="9">
+        <v>2</v>
+      </c>
       <c r="H49" s="5">
         <f>SUM(D49:G49)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I49" s="10"/>
-    </row>
-    <row r="50" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J49" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="K49" s="15"/>
+    </row>
+    <row r="50" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C50" s="11"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
+      <c r="D50" s="9">
+        <v>1</v>
+      </c>
+      <c r="E50" s="9">
+        <v>1</v>
+      </c>
+      <c r="F50" s="9">
+        <v>2</v>
+      </c>
+      <c r="G50" s="9">
+        <v>1</v>
+      </c>
       <c r="H50" s="5">
         <f>SUM(D50:G50)</f>
+        <v>5</v>
+      </c>
+      <c r="I50" s="10"/>
+      <c r="J50" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="K50" s="15"/>
+    </row>
+    <row r="51" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="11"/>
+      <c r="D51" s="9">
+        <v>2</v>
+      </c>
+      <c r="E51" s="9">
+        <v>2</v>
+      </c>
+      <c r="F51" s="9">
         <v>0</v>
       </c>
-      <c r="I50" s="10"/>
-    </row>
-    <row r="51" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C51" s="11"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
+      <c r="G51" s="9">
+        <v>1</v>
+      </c>
       <c r="H51" s="5">
         <f>SUM(D51:G51)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I51" s="10"/>
-    </row>
-    <row r="52" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J51" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="K51" s="15"/>
+    </row>
+    <row r="52" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="7" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C52" s="11"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
+      <c r="D52" s="9">
+        <v>1</v>
+      </c>
+      <c r="E52" s="9">
+        <v>1</v>
+      </c>
+      <c r="F52" s="9">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9">
+        <v>2</v>
+      </c>
       <c r="H52" s="5">
         <f>SUM(D52:G52)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I52" s="10"/>
-    </row>
-    <row r="53" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J52" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="K52" s="15"/>
+    </row>
+    <row r="53" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="7" t="s">
-        <v>108</v>
+        <v>8</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C53" s="11"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
+      <c r="D53" s="9">
+        <v>2</v>
+      </c>
+      <c r="E53" s="9">
+        <v>1</v>
+      </c>
+      <c r="F53" s="9">
+        <v>1</v>
+      </c>
+      <c r="G53" s="9">
+        <v>1</v>
+      </c>
       <c r="H53" s="5">
         <f>SUM(D53:G53)</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="10"/>
-    </row>
-    <row r="54" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="I53" s="13"/>
+      <c r="J53" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="7" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="C54" s="11"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
+      <c r="D54" s="9">
+        <v>2</v>
+      </c>
+      <c r="E54" s="9">
+        <v>1</v>
+      </c>
+      <c r="F54" s="9">
+        <v>1</v>
+      </c>
+      <c r="G54" s="9">
+        <v>1</v>
+      </c>
       <c r="H54" s="5">
         <f>SUM(D54:G54)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I54" s="10"/>
-    </row>
-    <row r="55" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J54" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="K54" s="15"/>
+    </row>
+    <row r="55" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="7" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="C55" s="11"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
+      <c r="D55" s="9">
+        <v>2</v>
+      </c>
+      <c r="E55" s="9">
+        <v>1</v>
+      </c>
+      <c r="F55" s="9">
+        <v>1</v>
+      </c>
+      <c r="G55" s="9">
+        <v>1</v>
+      </c>
       <c r="H55" s="5">
         <f>SUM(D55:G55)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I55" s="10"/>
-    </row>
-    <row r="56" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J55" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="7" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C56" s="11"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
+      <c r="D56" s="9">
+        <v>2</v>
+      </c>
+      <c r="E56" s="9">
+        <v>1</v>
+      </c>
+      <c r="F56" s="9">
+        <v>1</v>
+      </c>
+      <c r="G56" s="9">
+        <v>1</v>
+      </c>
       <c r="H56" s="5">
         <f>SUM(D56:G56)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I56" s="10"/>
-    </row>
-    <row r="57" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J56" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="K56" s="15"/>
+    </row>
+    <row r="57" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="7" t="s">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>83</v>
+        <v>233</v>
       </c>
       <c r="C57" s="11"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
+      <c r="D57" s="9">
+        <v>1</v>
+      </c>
+      <c r="E57" s="9">
+        <v>1</v>
+      </c>
+      <c r="F57" s="9">
+        <v>1</v>
+      </c>
+      <c r="G57" s="9">
+        <v>2</v>
+      </c>
       <c r="H57" s="5">
         <f>SUM(D57:G57)</f>
+        <v>5</v>
+      </c>
+      <c r="I57" s="10"/>
+      <c r="J57" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="K57" s="15"/>
+    </row>
+    <row r="58" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="11"/>
+      <c r="D58" s="9">
+        <v>2</v>
+      </c>
+      <c r="E58" s="9">
+        <v>2</v>
+      </c>
+      <c r="F58" s="9">
         <v>0</v>
       </c>
-      <c r="I57" s="10"/>
-    </row>
-    <row r="58" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C58" s="11"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
+      <c r="G58" s="9">
+        <v>1</v>
+      </c>
       <c r="H58" s="5">
         <f>SUM(D58:G58)</f>
+        <v>5</v>
+      </c>
+      <c r="I58" s="10"/>
+      <c r="J58" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="K58" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="11"/>
+      <c r="D59" s="9">
+        <v>2</v>
+      </c>
+      <c r="E59" s="9">
+        <v>2</v>
+      </c>
+      <c r="F59" s="9">
         <v>0</v>
       </c>
-      <c r="I58" s="10"/>
-    </row>
-    <row r="59" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
+      <c r="G59" s="9">
+        <v>1</v>
+      </c>
       <c r="H59" s="5">
         <f>SUM(D59:G59)</f>
+        <v>5</v>
+      </c>
+      <c r="I59" s="10"/>
+      <c r="J59" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="K59" s="15"/>
+    </row>
+    <row r="60" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60" s="11"/>
+      <c r="D60" s="9">
         <v>0</v>
       </c>
-      <c r="I59" s="10"/>
-    </row>
-    <row r="60" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="11"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
+      <c r="E60" s="9">
+        <v>2</v>
+      </c>
+      <c r="F60" s="9">
+        <v>1</v>
+      </c>
+      <c r="G60" s="9">
+        <v>2</v>
+      </c>
       <c r="H60" s="5">
         <f>SUM(D60:G60)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I60" s="10"/>
-    </row>
-    <row r="61" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J60" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="K60" s="15"/>
+    </row>
+    <row r="61" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="7" t="s">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="C61" s="11"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
+      <c r="D61" s="9">
+        <v>1</v>
+      </c>
+      <c r="E61" s="9">
+        <v>2</v>
+      </c>
+      <c r="F61" s="9">
+        <v>1</v>
+      </c>
+      <c r="G61" s="9">
+        <v>1</v>
+      </c>
       <c r="H61" s="5">
         <f>SUM(D61:G61)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I61" s="10"/>
-    </row>
-    <row r="62" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J61" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="K61" s="15"/>
+    </row>
+    <row r="62" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="7" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="C62" s="11"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
+      <c r="D62" s="9">
+        <v>1</v>
+      </c>
+      <c r="E62" s="9">
+        <v>2</v>
+      </c>
+      <c r="F62" s="9">
+        <v>1</v>
+      </c>
+      <c r="G62" s="9">
+        <v>1</v>
+      </c>
       <c r="H62" s="5">
         <f>SUM(D62:G62)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I62" s="10"/>
-    </row>
-    <row r="63" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J62" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="K62" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="7" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="C63" s="11"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
+      <c r="D63" s="9">
+        <v>2</v>
+      </c>
+      <c r="E63" s="9">
+        <v>1</v>
+      </c>
+      <c r="F63" s="9">
+        <v>1</v>
+      </c>
+      <c r="G63" s="9">
+        <v>1</v>
+      </c>
       <c r="H63" s="5">
         <f>SUM(D63:G63)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I63" s="10"/>
-    </row>
-    <row r="64" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J63" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="K63" s="15"/>
+    </row>
+    <row r="64" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="7" t="s">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="C64" s="11"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
+      <c r="D64" s="9">
+        <v>2</v>
+      </c>
+      <c r="E64" s="9">
+        <v>1</v>
+      </c>
+      <c r="F64" s="9">
+        <v>1</v>
+      </c>
+      <c r="G64" s="9">
+        <v>1</v>
+      </c>
       <c r="H64" s="5">
         <f>SUM(D64:G64)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I64" s="10"/>
-    </row>
-    <row r="65" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J64" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C65" s="11"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
+      <c r="D65" s="9">
+        <v>1</v>
+      </c>
+      <c r="E65" s="9">
+        <v>1</v>
+      </c>
+      <c r="F65" s="9">
+        <v>2</v>
+      </c>
+      <c r="G65" s="9">
+        <v>1</v>
+      </c>
       <c r="H65" s="5">
         <f>SUM(D65:G65)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I65" s="10"/>
-    </row>
-    <row r="66" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J65" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="K65" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="7" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="C66" s="11"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
+      <c r="D66" s="9">
+        <v>1</v>
+      </c>
+      <c r="E66" s="9">
+        <v>1</v>
+      </c>
+      <c r="F66" s="9">
+        <v>1</v>
+      </c>
+      <c r="G66" s="9">
+        <v>2</v>
+      </c>
       <c r="H66" s="5">
         <f>SUM(D66:G66)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I66" s="10"/>
-    </row>
-    <row r="67" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J66" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="K66" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C67" s="11"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
+      <c r="D67" s="9">
+        <v>1</v>
+      </c>
+      <c r="E67" s="9">
+        <v>1</v>
+      </c>
+      <c r="F67" s="9">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9">
+        <v>2</v>
+      </c>
       <c r="H67" s="5">
         <f>SUM(D67:G67)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I67" s="10"/>
-    </row>
-    <row r="68" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J67" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="K67" s="15"/>
+    </row>
+    <row r="68" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="7" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="C68" s="11"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
+      <c r="D68" s="9">
+        <v>1</v>
+      </c>
+      <c r="E68" s="9">
+        <v>1</v>
+      </c>
+      <c r="F68" s="9">
+        <v>1</v>
+      </c>
+      <c r="G68" s="9">
+        <v>1</v>
+      </c>
       <c r="H68" s="5">
         <f>SUM(D68:G68)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I68" s="10"/>
-    </row>
-    <row r="69" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J68" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="K68" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C69" s="11"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
+      <c r="D69" s="9">
+        <v>1</v>
+      </c>
+      <c r="E69" s="9">
+        <v>1</v>
+      </c>
+      <c r="F69" s="9">
+        <v>1</v>
+      </c>
+      <c r="G69" s="9">
+        <v>1</v>
+      </c>
       <c r="H69" s="5">
         <f>SUM(D69:G69)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I69" s="10"/>
-    </row>
-    <row r="70" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J69" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="K69" s="15"/>
+    </row>
+    <row r="70" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="7" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="C70" s="11"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
+      <c r="D70" s="9">
+        <v>1</v>
+      </c>
+      <c r="E70" s="9">
+        <v>1</v>
+      </c>
+      <c r="F70" s="9">
+        <v>1</v>
+      </c>
+      <c r="G70" s="9">
+        <v>1</v>
+      </c>
       <c r="H70" s="5">
         <f>SUM(D70:G70)</f>
+        <v>4</v>
+      </c>
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="15"/>
+    </row>
+    <row r="71" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="9">
+        <v>2</v>
+      </c>
+      <c r="E71" s="9">
+        <v>1</v>
+      </c>
+      <c r="F71" s="9">
         <v>0</v>
       </c>
-      <c r="I70" s="10"/>
-    </row>
-    <row r="71" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71" s="11"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
+      <c r="G71" s="9">
+        <v>1</v>
+      </c>
       <c r="H71" s="5">
         <f>SUM(D71:G71)</f>
+        <v>4</v>
+      </c>
+      <c r="I71" s="10"/>
+      <c r="J71" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="K71" s="15"/>
+    </row>
+    <row r="72" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="9">
         <v>0</v>
       </c>
-      <c r="I71" s="10"/>
-    </row>
-    <row r="72" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C72" s="11"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
+      <c r="E72" s="9">
+        <v>1</v>
+      </c>
+      <c r="F72" s="9">
+        <v>1</v>
+      </c>
+      <c r="G72" s="9">
+        <v>2</v>
+      </c>
       <c r="H72" s="5">
         <f>SUM(D72:G72)</f>
+        <v>4</v>
+      </c>
+      <c r="I72" s="10"/>
+      <c r="J72" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="11"/>
+      <c r="D73" s="9">
+        <v>2</v>
+      </c>
+      <c r="E73" s="9">
+        <v>1</v>
+      </c>
+      <c r="F73" s="9">
+        <v>1</v>
+      </c>
+      <c r="G73" s="9">
         <v>0</v>
       </c>
-      <c r="I72" s="10"/>
-    </row>
-    <row r="73" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73" s="11"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
       <c r="H73" s="5">
         <f>SUM(D73:G73)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I73" s="10"/>
-    </row>
-    <row r="74" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J73" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="K73" s="15"/>
+    </row>
+    <row r="74" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="7" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C74" s="11"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
+      <c r="D74" s="9">
+        <v>1</v>
+      </c>
+      <c r="E74" s="9">
+        <v>1</v>
+      </c>
+      <c r="F74" s="9">
+        <v>1</v>
+      </c>
+      <c r="G74" s="9">
+        <v>1</v>
+      </c>
       <c r="H74" s="5">
         <f>SUM(D74:G74)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I74" s="10"/>
-    </row>
-    <row r="75" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+    </row>
+    <row r="75" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="7" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="C75" s="11"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
+      <c r="D75" s="9">
+        <v>1</v>
+      </c>
+      <c r="E75" s="9">
+        <v>1</v>
+      </c>
+      <c r="F75" s="9">
+        <v>1</v>
+      </c>
+      <c r="G75" s="9">
+        <v>1</v>
+      </c>
       <c r="H75" s="5">
         <f>SUM(D75:G75)</f>
+        <v>4</v>
+      </c>
+      <c r="I75" s="10"/>
+      <c r="J75" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K75" s="15"/>
+    </row>
+    <row r="76" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C76" s="11"/>
+      <c r="D76" s="9">
+        <v>2</v>
+      </c>
+      <c r="E76" s="9">
         <v>0</v>
       </c>
-      <c r="I75" s="10"/>
-    </row>
-    <row r="76" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C76" s="11"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
+      <c r="F76" s="9">
+        <v>1</v>
+      </c>
+      <c r="G76" s="9">
+        <v>1</v>
+      </c>
       <c r="H76" s="5">
         <f>SUM(D76:G76)</f>
+        <v>4</v>
+      </c>
+      <c r="I76" s="10"/>
+      <c r="J76" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K76" s="15"/>
+    </row>
+    <row r="77" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="C77" s="11"/>
+      <c r="D77" s="9">
+        <v>2</v>
+      </c>
+      <c r="E77" s="9">
         <v>0</v>
       </c>
-      <c r="I76" s="10"/>
-    </row>
-    <row r="77" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C77" s="11"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
+      <c r="F77" s="9">
+        <v>1</v>
+      </c>
+      <c r="G77" s="9">
+        <v>1</v>
+      </c>
       <c r="H77" s="5">
         <f>SUM(D77:G77)</f>
+        <v>4</v>
+      </c>
+      <c r="I77" s="10"/>
+      <c r="J77" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="K77" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="11"/>
+      <c r="D78" s="9">
+        <v>2</v>
+      </c>
+      <c r="E78" s="9">
         <v>0</v>
       </c>
-      <c r="I77" s="10"/>
-    </row>
-    <row r="78" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C78" s="11"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
+      <c r="F78" s="9">
+        <v>1</v>
+      </c>
+      <c r="G78" s="9">
+        <v>1</v>
+      </c>
       <c r="H78" s="5">
         <f>SUM(D78:G78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I78" s="10"/>
-    </row>
-    <row r="79" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J78" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="K78" s="15"/>
+    </row>
+    <row r="79" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="7" t="s">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>107</v>
+        <v>275</v>
       </c>
       <c r="C79" s="11"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
+      <c r="D79" s="9">
+        <v>1</v>
+      </c>
+      <c r="E79" s="9">
+        <v>1</v>
+      </c>
+      <c r="F79" s="9">
+        <v>1</v>
+      </c>
+      <c r="G79" s="9">
+        <v>1</v>
+      </c>
       <c r="H79" s="5">
         <f>SUM(D79:G79)</f>
+        <v>4</v>
+      </c>
+      <c r="I79" s="10"/>
+      <c r="J79" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="K79" s="15"/>
+    </row>
+    <row r="80" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C80" s="11"/>
+      <c r="D80" s="9">
+        <v>1</v>
+      </c>
+      <c r="E80" s="9">
         <v>0</v>
       </c>
-      <c r="I79" s="10"/>
-    </row>
-    <row r="80" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="11"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
+      <c r="F80" s="9">
+        <v>1</v>
+      </c>
+      <c r="G80" s="9">
+        <v>1</v>
+      </c>
       <c r="H80" s="5">
         <f>SUM(D80:G80)</f>
+        <v>3</v>
+      </c>
+      <c r="I80" s="10"/>
+      <c r="J80" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="K80" s="15"/>
+    </row>
+    <row r="81" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81" s="11"/>
+      <c r="D81" s="9">
+        <v>1</v>
+      </c>
+      <c r="E81" s="9">
         <v>0</v>
       </c>
-      <c r="I80" s="10"/>
-    </row>
-    <row r="81" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C81" s="11"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
+      <c r="F81" s="9">
+        <v>1</v>
+      </c>
+      <c r="G81" s="9">
+        <v>1</v>
+      </c>
       <c r="H81" s="5">
         <f>SUM(D81:G81)</f>
+        <v>3</v>
+      </c>
+      <c r="I81" s="10"/>
+      <c r="J81" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="11"/>
+      <c r="D82" s="9">
+        <v>1</v>
+      </c>
+      <c r="E82" s="9">
         <v>0</v>
       </c>
-      <c r="I81" s="10"/>
-    </row>
-    <row r="82" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="C82" s="11"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
+      <c r="F82" s="9">
+        <v>1</v>
+      </c>
+      <c r="G82" s="9">
+        <v>1</v>
+      </c>
       <c r="H82" s="5">
         <f>SUM(D82:G82)</f>
+        <v>3</v>
+      </c>
+      <c r="I82" s="10"/>
+      <c r="J82" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="K82" s="15"/>
+    </row>
+    <row r="83" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83" s="11"/>
+      <c r="D83" s="9">
+        <v>1</v>
+      </c>
+      <c r="E83" s="9">
+        <v>1</v>
+      </c>
+      <c r="F83" s="9">
         <v>0</v>
       </c>
-      <c r="I82" s="10"/>
-    </row>
-    <row r="83" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C83" s="11"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
+      <c r="G83" s="9">
+        <v>1</v>
+      </c>
       <c r="H83" s="5">
         <f>SUM(D83:G83)</f>
+        <v>3</v>
+      </c>
+      <c r="I83" s="10"/>
+      <c r="J83" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="K83" s="15"/>
+    </row>
+    <row r="84" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="9">
+        <v>1</v>
+      </c>
+      <c r="E84" s="9">
+        <v>1</v>
+      </c>
+      <c r="F84" s="9">
         <v>0</v>
       </c>
-      <c r="I83" s="10"/>
-    </row>
-    <row r="84" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C84" s="11"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
+      <c r="G84" s="9">
+        <v>1</v>
+      </c>
       <c r="H84" s="5">
         <f>SUM(D84:G84)</f>
+        <v>3</v>
+      </c>
+      <c r="I84" s="10"/>
+      <c r="J84" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="K84" s="15"/>
+    </row>
+    <row r="85" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85" s="11"/>
+      <c r="D85" s="9">
+        <v>2</v>
+      </c>
+      <c r="E85" s="9">
         <v>0</v>
       </c>
-      <c r="I84" s="10"/>
-    </row>
-    <row r="85" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C85" s="11"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
+      <c r="F85" s="9">
+        <v>0</v>
+      </c>
+      <c r="G85" s="9">
+        <v>1</v>
+      </c>
       <c r="H85" s="5">
         <f>SUM(D85:G85)</f>
+        <v>3</v>
+      </c>
+      <c r="I85" s="10"/>
+      <c r="J85" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="K85" s="15"/>
+    </row>
+    <row r="86" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C86" s="11"/>
+      <c r="D86" s="9">
         <v>0</v>
       </c>
-      <c r="I85" s="10"/>
-    </row>
-    <row r="86" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C86" s="11"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
+      <c r="E86" s="9">
+        <v>1</v>
+      </c>
+      <c r="F86" s="9">
+        <v>1</v>
+      </c>
+      <c r="G86" s="9">
+        <v>1</v>
+      </c>
       <c r="H86" s="5">
         <f>SUM(D86:G86)</f>
+        <v>3</v>
+      </c>
+      <c r="I86" s="10"/>
+      <c r="J86" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="K86" s="15"/>
+    </row>
+    <row r="87" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C87" s="11"/>
+      <c r="D87" s="9">
+        <v>1</v>
+      </c>
+      <c r="E87" s="9">
+        <v>1</v>
+      </c>
+      <c r="F87" s="9">
         <v>0</v>
       </c>
-      <c r="I86" s="10"/>
-    </row>
-    <row r="87" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C87" s="11"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
+      <c r="G87" s="9">
+        <v>1</v>
+      </c>
       <c r="H87" s="5">
         <f>SUM(D87:G87)</f>
+        <v>3</v>
+      </c>
+      <c r="I87" s="10"/>
+      <c r="J87" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="K87" s="15"/>
+    </row>
+    <row r="88" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="11"/>
+      <c r="D88" s="9">
+        <v>1</v>
+      </c>
+      <c r="E88" s="9">
         <v>0</v>
       </c>
-      <c r="I87" s="10"/>
-    </row>
-    <row r="88" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" s="11"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
+      <c r="F88" s="9">
+        <v>1</v>
+      </c>
+      <c r="G88" s="9">
+        <v>1</v>
+      </c>
       <c r="H88" s="5">
         <f>SUM(D88:G88)</f>
+        <v>3</v>
+      </c>
+      <c r="I88" s="10"/>
+      <c r="J88" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="K88" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C89" s="11"/>
+      <c r="D89" s="9">
+        <v>1</v>
+      </c>
+      <c r="E89" s="9">
+        <v>1</v>
+      </c>
+      <c r="F89" s="9">
         <v>0</v>
       </c>
-      <c r="I88" s="10"/>
+      <c r="G89" s="9">
+        <v>1</v>
+      </c>
+      <c r="H89" s="5">
+        <f>SUM(D89:G89)</f>
+        <v>3</v>
+      </c>
+      <c r="I89" s="10"/>
+      <c r="J89" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="K89" s="15"/>
+    </row>
+    <row r="90" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C90" s="11"/>
+      <c r="D90" s="9">
+        <v>2</v>
+      </c>
+      <c r="E90" s="9">
+        <v>0</v>
+      </c>
+      <c r="F90" s="9">
+        <v>0</v>
+      </c>
+      <c r="G90" s="9">
+        <v>1</v>
+      </c>
+      <c r="H90" s="5">
+        <f>SUM(D90:G90)</f>
+        <v>3</v>
+      </c>
+      <c r="I90" s="10"/>
+      <c r="J90" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="K90" s="15"/>
+    </row>
+    <row r="91" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C91" s="11"/>
+      <c r="D91" s="9">
+        <v>1</v>
+      </c>
+      <c r="E91" s="9">
+        <v>1</v>
+      </c>
+      <c r="F91" s="9">
+        <v>0</v>
+      </c>
+      <c r="G91" s="9">
+        <v>1</v>
+      </c>
+      <c r="H91" s="5">
+        <f>SUM(D91:G91)</f>
+        <v>3</v>
+      </c>
+      <c r="I91" s="10"/>
+      <c r="J91" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="K91" s="15"/>
+    </row>
+    <row r="92" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C92" s="11"/>
+      <c r="D92" s="9">
+        <v>1</v>
+      </c>
+      <c r="E92" s="9">
+        <v>0</v>
+      </c>
+      <c r="F92" s="9">
+        <v>0</v>
+      </c>
+      <c r="G92" s="9">
+        <v>1</v>
+      </c>
+      <c r="H92" s="5">
+        <f>SUM(D92:G92)</f>
+        <v>2</v>
+      </c>
+      <c r="I92" s="10"/>
+      <c r="J92" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="K92" s="15"/>
+    </row>
+    <row r="95" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B95" s="18">
+        <f>COUNTIF(H:H,"&gt;6")</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="B96" s="18">
+        <f>COUNTIFS(H:H,"&gt;3",H:H,"&lt;6")</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B97" s="18">
+        <f>COUNTIFS(H:H,"&gt;0",H:H,"&lt;4")</f>
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I88" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I88">
-      <sortCondition ref="B1:B88"/>
+  <autoFilter ref="A1:I92" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I92">
+      <sortCondition descending="1" ref="H1:H92"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="B2:K69 B70:I71 K70:K71 B72:K92">
+    <cfRule type="expression" dxfId="8" priority="7" stopIfTrue="1">
+      <formula>AND($H2&lt;4,$H2&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
+      <formula>AND($H2&gt;3,$H2&lt;7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>$H2&gt;6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J71">
+    <cfRule type="expression" dxfId="5" priority="13" stopIfTrue="1">
+      <formula>AND($H70&lt;4,$H70&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="14" stopIfTrue="1">
+      <formula>AND($H70&gt;3,$H70&lt;7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="15">
+      <formula>$H70&gt;6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J70">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+      <formula>AND($H70&lt;4,$H70&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>AND($H70&gt;3,$H70&lt;7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>$H70&gt;6</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:G88" xr:uid="{80B27CD6-D622-CF47-AFE8-3311BE5C0CBA}">
-      <formula1>0</formula1>
-      <formula2>2</formula2>
-    </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Topical Relevance (0–2)" prompt="Question To what extent does the article substantively address semantic interoperability in public-sector or cross-organizational contexts?  Scoring_x000a_0: Semantic interoperability is not a substantive focus or is only mentioned incidentally._x000a_1: Semantic inte" sqref="D1" xr:uid="{13ADD9E6-288C-C240-9541-D555ED21F8C3}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Analytical Contribution (0–2)" prompt="What type of analytical contribution does the article make beyond description?" sqref="E1" xr:uid="{41BDF49C-BD9C-7D4E-A4A0-57F700C5B21F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Level of Abstraction and Transfe" prompt="To what extent are the insights abstracted from the specific empirical context and articulated in a reusable form?_x000a_" sqref="F1" xr:uid="{E6E0F246-078F-E34A-9AF5-BBF4FE34BF46}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Conceptual and Methodological Ri" prompt="How clearly and coherently is the contribution conceptually and methodologically grounded?_x000a_" sqref="G1" xr:uid="{4B6A5BD2-5457-7144-9DDC-E9CDC57FBACE}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:G92" xr:uid="{80B27CD6-D622-CF47-AFE8-3311BE5C0CBA}">
+      <formula1>0</formula1>
+      <formula2>2</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -3612,7 +5220,7 @@
           <x14:formula1>
             <xm:f>Exclusiecriteria!$A$1:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C88</xm:sqref>
+          <xm:sqref>C2:C92</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3631,27 +5239,27 @@
     <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>185</v>
       </c>

--- a/04_fulltext/fullTextScreening.xlsx
+++ b/04_fulltext/fullTextScreening.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arjen/kDrive/Obsidian/Literature Review MDIM/04_fulltext/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3DDE09-82A1-8547-A5DB-D5DEF28A6990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E68B51E-B3BC-9B4C-AA37-9990B104CB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Full Text Scores" sheetId="1" r:id="rId1"/>
+    <sheet name="01_CoreScreening" sheetId="1" r:id="rId1"/>
     <sheet name="Exclusiecriteria" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full Text Scores'!$A$1:$I$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_CoreScreening'!$A$1:$I$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2408,7 +2408,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="5">
-        <f>SUM(D2:G2)</f>
+        <f t="shared" ref="H2:H33" si="0">SUM(D2:G2)</f>
         <v>8</v>
       </c>
       <c r="I2" s="6"/>
@@ -2436,7 +2436,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <f>SUM(D3:G3)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I3" s="10"/>
@@ -2464,7 +2464,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <f>SUM(D4:G4)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I4" s="10"/>
@@ -2494,7 +2494,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <f>SUM(D5:G5)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I5" s="10"/>
@@ -2524,7 +2524,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <f>SUM(D6:G6)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I6" s="10"/>
@@ -2554,7 +2554,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <f>SUM(D7:G7)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I7" s="10"/>
@@ -2584,7 +2584,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="5">
-        <f>SUM(D8:G8)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I8" s="10"/>
@@ -2614,7 +2614,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <f>SUM(D9:G9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I9" s="10"/>
@@ -2644,7 +2644,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="5">
-        <f>SUM(D10:G10)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I10" s="10"/>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="5">
-        <f>SUM(D11:G11)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I11" s="10"/>
@@ -2704,7 +2704,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="5">
-        <f>SUM(D12:G12)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I12" s="10"/>
@@ -2734,7 +2734,7 @@
         <v>2</v>
       </c>
       <c r="H13" s="5">
-        <f>SUM(D13:G13)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I13" s="10"/>
@@ -2764,7 +2764,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="5">
-        <f>SUM(D14:G14)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I14" s="10"/>
@@ -2794,7 +2794,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="5">
-        <f>SUM(D15:G15)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I15" s="10"/>
@@ -2824,7 +2824,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="5">
-        <f>SUM(D16:G16)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I16" s="10"/>
@@ -2854,7 +2854,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="5">
-        <f>SUM(D17:G17)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I17" s="10"/>
@@ -2882,7 +2882,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="5">
-        <f>SUM(D18:G18)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I18" s="10"/>
@@ -2910,7 +2910,7 @@
         <v>2</v>
       </c>
       <c r="H19" s="5">
-        <f>SUM(D19:G19)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I19" s="10"/>
@@ -2940,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="5">
-        <f>SUM(D20:G20)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I20" s="10"/>
@@ -2968,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="5">
-        <f>SUM(D21:G21)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I21" s="10"/>
@@ -2998,7 +2998,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="5">
-        <f>SUM(D22:G22)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I22" s="10"/>
@@ -3028,7 +3028,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="5">
-        <f>SUM(D23:G23)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I23" s="10"/>
@@ -3058,7 +3058,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="5">
-        <f>SUM(D24:G24)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I24" s="10"/>
@@ -3088,7 +3088,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="5">
-        <f>SUM(D25:G25)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I25" s="10"/>
@@ -3118,7 +3118,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="5">
-        <f>SUM(D26:G26)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I26" s="10"/>
@@ -3148,7 +3148,7 @@
         <v>2</v>
       </c>
       <c r="H27" s="5">
-        <f>SUM(D27:G27)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I27" s="10"/>
@@ -3176,7 +3176,7 @@
         <v>2</v>
       </c>
       <c r="H28" s="5">
-        <f>SUM(D28:G28)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I28" s="10"/>
@@ -3206,7 +3206,7 @@
         <v>2</v>
       </c>
       <c r="H29" s="5">
-        <f>SUM(D29:G29)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I29" s="10"/>
@@ -3236,7 +3236,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="5">
-        <f>SUM(D30:G30)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I30" s="10"/>
@@ -3266,7 +3266,7 @@
         <v>2</v>
       </c>
       <c r="H31" s="5">
-        <f>SUM(D31:G31)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I31" s="10"/>
@@ -3296,7 +3296,7 @@
         <v>2</v>
       </c>
       <c r="H32" s="5">
-        <f>SUM(D32:G32)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I32" s="10"/>
@@ -3324,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="5">
-        <f>SUM(D33:G33)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="I33" s="10"/>
@@ -3352,7 +3352,7 @@
         <v>2</v>
       </c>
       <c r="H34" s="5">
-        <f>SUM(D34:G34)</f>
+        <f t="shared" ref="H34:H65" si="1">SUM(D34:G34)</f>
         <v>7</v>
       </c>
       <c r="I34" s="10"/>
@@ -3382,7 +3382,7 @@
         <v>2</v>
       </c>
       <c r="H35" s="5">
-        <f>SUM(D35:G35)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="I35" s="10"/>
@@ -3410,7 +3410,7 @@
         <v>2</v>
       </c>
       <c r="H36" s="5">
-        <f>SUM(D36:G36)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="I36" s="10"/>
@@ -3442,7 +3442,7 @@
         <v>2</v>
       </c>
       <c r="H37" s="5">
-        <f>SUM(D37:G37)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I37" s="10"/>
@@ -3474,7 +3474,7 @@
         <v>2</v>
       </c>
       <c r="H38" s="5">
-        <f>SUM(D38:G38)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I38" s="10"/>
@@ -3504,7 +3504,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="5">
-        <f>SUM(D39:G39)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I39" s="10"/>
@@ -3536,7 +3536,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="5">
-        <f>SUM(D40:G40)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I40" s="10"/>
@@ -3566,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="5">
-        <f>SUM(D41:G41)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I41" s="10"/>
@@ -3596,7 +3596,7 @@
         <v>2</v>
       </c>
       <c r="H42" s="5">
-        <f>SUM(D42:G42)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I42" s="10"/>
@@ -3628,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="5">
-        <f>SUM(D43:G43)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I43" s="10"/>
@@ -3658,7 +3658,7 @@
         <v>2</v>
       </c>
       <c r="H44" s="5">
-        <f>SUM(D44:G44)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I44" s="10"/>
@@ -3690,7 +3690,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="5">
-        <f>SUM(D45:G45)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I45" s="10"/>
@@ -3720,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="5">
-        <f>SUM(D46:G46)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I46" s="10"/>
@@ -3750,7 +3750,7 @@
         <v>2</v>
       </c>
       <c r="H47" s="5">
-        <f>SUM(D47:G47)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I47" s="10"/>
@@ -3782,7 +3782,7 @@
         <v>2</v>
       </c>
       <c r="H48" s="5">
-        <f>SUM(D48:G48)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I48" s="10"/>
@@ -3812,7 +3812,7 @@
         <v>2</v>
       </c>
       <c r="H49" s="5">
-        <f>SUM(D49:G49)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I49" s="10"/>
@@ -3842,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="5">
-        <f>SUM(D50:G50)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I50" s="10"/>
@@ -3872,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="5">
-        <f>SUM(D51:G51)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I51" s="10"/>
@@ -3902,7 +3902,7 @@
         <v>2</v>
       </c>
       <c r="H52" s="5">
-        <f>SUM(D52:G52)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I52" s="10"/>
@@ -3932,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="5">
-        <f>SUM(D53:G53)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I53" s="13"/>
@@ -3964,7 +3964,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="5">
-        <f>SUM(D54:G54)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I54" s="10"/>
@@ -3994,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="5">
-        <f>SUM(D55:G55)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I55" s="10"/>
@@ -4026,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="5">
-        <f>SUM(D56:G56)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I56" s="10"/>
@@ -4056,7 +4056,7 @@
         <v>2</v>
       </c>
       <c r="H57" s="5">
-        <f>SUM(D57:G57)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I57" s="10"/>
@@ -4086,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="5">
-        <f>SUM(D58:G58)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I58" s="10"/>
@@ -4118,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="5">
-        <f>SUM(D59:G59)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I59" s="10"/>
@@ -4148,7 +4148,7 @@
         <v>2</v>
       </c>
       <c r="H60" s="5">
-        <f>SUM(D60:G60)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I60" s="10"/>
@@ -4178,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="5">
-        <f>SUM(D61:G61)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I61" s="10"/>
@@ -4208,7 +4208,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="5">
-        <f>SUM(D62:G62)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I62" s="10"/>
@@ -4240,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="5">
-        <f>SUM(D63:G63)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I63" s="10"/>
@@ -4270,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="5">
-        <f>SUM(D64:G64)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I64" s="10"/>
@@ -4302,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="5">
-        <f>SUM(D65:G65)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I65" s="10"/>
@@ -4334,7 +4334,7 @@
         <v>2</v>
       </c>
       <c r="H66" s="5">
-        <f>SUM(D66:G66)</f>
+        <f t="shared" ref="H66:H97" si="2">SUM(D66:G66)</f>
         <v>5</v>
       </c>
       <c r="I66" s="10"/>
@@ -4366,7 +4366,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="5">
-        <f>SUM(D67:G67)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="I67" s="10"/>
@@ -4396,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="5">
-        <f>SUM(D68:G68)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I68" s="10"/>
@@ -4428,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="5">
-        <f>SUM(D69:G69)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I69" s="10"/>
@@ -4458,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="5">
-        <f>SUM(D70:G70)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I70" s="10"/>
@@ -4486,7 +4486,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="5">
-        <f>SUM(D71:G71)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I71" s="10"/>
@@ -4516,7 +4516,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="5">
-        <f>SUM(D72:G72)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I72" s="10"/>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="5">
-        <f>SUM(D73:G73)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I73" s="10"/>
@@ -4578,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="5">
-        <f>SUM(D74:G74)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I74" s="10"/>
@@ -4606,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="5">
-        <f>SUM(D75:G75)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I75" s="10"/>
@@ -4636,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="5">
-        <f>SUM(D76:G76)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I76" s="10"/>
@@ -4666,7 +4666,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="5">
-        <f>SUM(D77:G77)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I77" s="10"/>
@@ -4698,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="5">
-        <f>SUM(D78:G78)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I78" s="10"/>
@@ -4728,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="5">
-        <f>SUM(D79:G79)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I79" s="10"/>
@@ -4758,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="5">
-        <f>SUM(D80:G80)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I80" s="10"/>
@@ -4788,7 +4788,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="5">
-        <f>SUM(D81:G81)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I81" s="10"/>
@@ -4820,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="5">
-        <f>SUM(D82:G82)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I82" s="10"/>
@@ -4850,7 +4850,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="5">
-        <f>SUM(D83:G83)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I83" s="10"/>
@@ -4880,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="5">
-        <f>SUM(D84:G84)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I84" s="10"/>
@@ -4910,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="5">
-        <f>SUM(D85:G85)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I85" s="10"/>
@@ -4940,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="5">
-        <f>SUM(D86:G86)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I86" s="10"/>
@@ -4970,7 +4970,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="5">
-        <f>SUM(D87:G87)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I87" s="10"/>
@@ -5000,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="5">
-        <f>SUM(D88:G88)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I88" s="10"/>
@@ -5032,7 +5032,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="5">
-        <f>SUM(D89:G89)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I89" s="10"/>
@@ -5062,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="5">
-        <f>SUM(D90:G90)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I90" s="10"/>
@@ -5092,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="5">
-        <f>SUM(D91:G91)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I91" s="10"/>
@@ -5122,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="5">
-        <f>SUM(D92:G92)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I92" s="10"/>
@@ -5175,25 +5175,25 @@
       <formula>$H2&gt;6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J71">
-    <cfRule type="expression" dxfId="5" priority="13" stopIfTrue="1">
+  <conditionalFormatting sqref="J70">
+    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
       <formula>AND($H70&lt;4,$H70&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="2" stopIfTrue="1">
       <formula>AND($H70&gt;3,$H70&lt;7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="15">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$H70&gt;6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J70">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="J71">
+    <cfRule type="expression" dxfId="2" priority="13" stopIfTrue="1">
       <formula>AND($H70&lt;4,$H70&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="14" stopIfTrue="1">
       <formula>AND($H70&gt;3,$H70&lt;7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>$H70&gt;6</formula>
     </cfRule>
   </conditionalFormatting>
